--- a/artfynd/A 32067-2026 artfynd.xlsx
+++ b/artfynd/A 32067-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135579943</v>
       </c>
       <c r="B2" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>135579944</v>
       </c>
       <c r="B3" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32067-2026 artfynd.xlsx
+++ b/artfynd/A 32067-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135579943</v>
       </c>
       <c r="B2" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>135579944</v>
       </c>
       <c r="B3" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
